--- a/NOP_BAI_DRIVE/Mau_02_Bug_Manifest.xlsx
+++ b/NOP_BAI_DRIVE/Mau_02_Bug_Manifest.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug Manifest" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug_Manifest" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,7 +29,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001F4E79"/>
-      <sz val="14"/>
+      <sz val="15"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -64,7 +64,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -79,12 +79,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -114,10 +129,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -126,16 +141,31 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -503,36 +533,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BẢNG DANH MỤC LỖI PHẦN MỀM (BUG MANIFEST) - SMARTCALC PRO</t>
+          <t>BẢNG DANH MỤC LỖI CÀI SẴN (BUG MANIFEST) - HỌC PHẦN ĐÁNH GIÁ HIỆU NĂNG CSE3066</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Môn học: Đánh giá hiệu năng CSE3066</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Sinh viên: Phạm Văn Quang - MSSV: 23110342</t>
+          <t>Sinh viên thực hiện: Phạm Văn Quang - MSSV: 23110342</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Hệ thống: SmartCalc Pro (Web Application &amp; Testing)</t>
         </is>
       </c>
     </row>
@@ -542,767 +576,1168 @@
           <t>GitHub Repo: https://github.com/QUANGPV021/calculator-qa-testing</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Demo Pages: https://quangpv021.github.io/calculator-qa-testing/</t>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Website Live: https://quangpv021.github.io/calculator-qa-testing/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Bug ID</t>
+          <t>Mã lỗi</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Phân loại</t>
+          <t>Loại lỗi</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Mô tả lỗi (Title)</t>
+          <t>Mức nghiêm trọng</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Mức độ (Severity)</t>
+          <t>Chức năng / Luồng</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Các bước tái hiện (Steps)</t>
+          <t>Vị trí (màn hình / URL)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Kết quả thực tế (Actual)</t>
+          <t>Yêu cầu SRS bị vi phạm</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Kết quả kỳ vọng (Expected)</t>
+          <t>Mô tả lỗi</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Dòng code lỗi (app.js)</t>
+          <t>Các bước tái hiện</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Giải pháp sửa (Patch)</t>
+          <t>Kết quả mong đợi (theo SRS)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Kết quả thực tế</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Bằng chứng (Link ảnh/video)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>File chứa lỗi</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>BUG-01</t>
+          <t>SEED-01</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Trong đặc tả (FR-07)</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Sai số dấu phẩy động: 0.1 + 0.2 ra 0.30000000000000004</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Nhập 0.1 -&gt; bấm + -&gt; nhập 0.2 -&gt; bấm =</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>0.30000000000000004</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>0.3 (chuẩn hóa làm tròn số thực)</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>Dòng 359: return firstVal + secondVal;</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>return parseFloat((firstVal + secondVal).toFixed(12));</t>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Tính toán số học</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Màn hình chính / app.js</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>FR-07 (Độ chính xác số học)</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Sai số dấu phẩy động IEEE-754: 0.1 + 0.2 ra 0.30000000000000004</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>1. Nhập 0.1
+2. Bấm +
+3. Nhập 0.2
+4. Bấm =</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Màn hình hiển thị 0.3 chuẩn</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Màn hình hiển thị 0.30000000000000004</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>https://quangpv021.github.io/calculator-qa-testing/assets/evidence_bug01.png</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>app.js (performRawCalculation)</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>Trong đặc tả</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>BUG-02</t>
+          <t>SEED-02</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Trong đặc tả (FR-04)</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Cho phép nhập nhiều dấu chấm thập phân trong 1 số (5.2.3)</t>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Major</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Nhập 5 -&gt; bấm . -&gt; nhập 2 -&gt; bấm . -&gt; nhập 3</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Màn hình hiển thị 5.2.3</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Chỉ cho phép duy nhất 1 dấu chấm (5.23)</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>Dòng 321: if (state.currentInput.endsWith('.'))</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>if (state.currentInput.includes('.')) return;</t>
+          <t>Nhập liệu số thập phân</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Màn hình chính / app.js</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>FR-04 (Dấu chấm thập phân)</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Cho phép nhập nhiều dấu chấm thập phân trong cùng 1 toán hạng (5.2.3)</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>1. Nhập 5 -&gt; Bấm .
+2. Nhập 2 -&gt; Bấm .
+3. Nhập 3</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Chỉ cho phép 1 dấu chấm (5.23)</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Màn hình hiển thị chuỗi dị tật 5.2.3</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>https://quangpv021.github.io/calculator-qa-testing/assets/evidence_bug02.png</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>app.js (inputDecimal)</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>Trong đặc tả</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>BUG-03</t>
+          <t>SEED-03</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Trong đặc tả (FR-09)</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Phép chia cho 0 trả về Infinity thay vì báo lỗi</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Nhập 9 -&gt; bấm ÷ -&gt; nhập 0 -&gt; bấm =</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Hiển thị 'Infinity'</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Thông báo lỗi: 'Cannot divide by 0'</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>Dòng 371: if (secondVal === 0) return Infinity;</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>return 'Cannot divide by 0'; khóa thao tác tính.</t>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Phép chia số học</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Màn hình chính / app.js</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>FR-09 (Phép chia cho 0)</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Phép chia cho 0 trả về chuỗi Infinity thay vì hiển thị thông báo lỗi</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>1. Nhập 9 -&gt; Bấm ÷
+2. Nhập 0 -&gt; Bấm =</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Báo lỗi thân thiện 'Cannot divide by 0' và khóa tính tiếp</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Màn hình hiển thị 'Infinity'</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>https://quangpv021.github.io/calculator-qa-testing/assets/evidence_bug03.png</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>app.js (performRawCalculation)</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>Trong đặc tả</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>BUG-04</t>
+          <t>SEED-04</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Trong đặc tả (FR-08)</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Vi phạm thứ tự ưu tiên BODMAS: 2 + 3 * 4 ra 20</t>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Major</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Nhập 2 -&gt; bấm + -&gt; nhập 3 -&gt; bấm × -&gt; nhập 4 -&gt; =</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Tính tuần tự ra 20</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Kết quả đúng toán học là 14 (nhân chia trước)</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>Dòng 342: tính dồn ngay khi gặp toán tử mới</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>Áp dụng thuật toán Shunting-yard parse biểu thức.</t>
+          <t>Ưu tiên toán học</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Màn hình chính / app.js</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>FR-08 (Thứ tự BODMAS)</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Vi phạm thứ tự ưu tiên: 2 + 3 * 4 ra 20 thay vì 14</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>1. Nhập 2 + 3 × 4 =</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Kết quả là 14 (nhân chia trước cộng trừ sau)</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Tính tuần tự ra 20 ((2 + 3) * 4)</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>https://quangpv021.github.io/calculator-qa-testing/assets/evidence_bug04.png</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>app.js (handleOperator)</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>Trong đặc tả</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>BUG-05</t>
+          <t>SEED-05</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Trong đặc tả (FR-11)</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Căn bậc hai số âm xuất hiện chuỗi 'NaN'</t>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Major</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Nhập 9 -&gt; bấm ± (thành -9) -&gt; bấm √</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Hiển thị chuỗi 'NaN'</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+          <t>Hàm nâng cao căn bậc hai</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Màn hình chính / app.js</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>FR-11 (Căn bậc hai)</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Căn bậc hai số âm xuất hiện chuỗi 'NaN' gây lỗi hiển thị</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>1. Nhập 9 -&gt; Bấm ± (-9)
+2. Bấm √</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Báo lỗi hợp lệ 'Invalid Input'</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>Dòng 424: Math.sqrt(val) thiếu kiểm tra val &lt; 0</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>if (val &lt; 0) return 'Invalid Input';</t>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Màn hình xuất hiện chuỗi 'NaN'</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>https://quangpv021.github.io/calculator-qa-testing/assets/evidence_bug05.png</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>app.js (calcSquareRoot)</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>Trong đặc tả</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>BUG-06</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Trong đặc tả (FR-03)</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Cho phép nhập nhiều số 0 vô nghĩa ở đầu (0008)</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Bấm 0 liên tiếp 3 lần -&gt; bấm 8</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Hiển thị '0008'</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Tự động chuẩn hóa thành '8'</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Dòng 297: state.currentInput = '00';</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>state.currentInput = digit;</t>
+          <t>SEED-06</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Màn hình hiển thị</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Giao diện màn hình / style.css</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>FR-05 (Giới hạn hiển thị)</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Tràn viền màn hình (Layout Overflow) khi nhập chuỗi số dài hơn 16 ký tự</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>1. Nhấn liên tục 25 phím số 9</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Giới hạn 16 số hoặc tự co nhỏ cỡ chữ dạng e-notation</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Dãy số tràn vượt ra khỏi khung máy tính làm vỡ giao diện</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>https://quangpv021.github.io/calculator-qa-testing/assets/evidence_bug06.png</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>style.css (.screen-main)</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>Trong đặc tả</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>BUG-07</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Trong đặc tả (FR-05)</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Tràn viền màn hình máy tính khi nhập quá 16 chữ số</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Nhập liên tục 25 chữ số 9</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Chữ số tràn vỡ ra ngoài khung máy tính</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Giới hạn 15-16 số hoặc tự co chữ / e-notation</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>Thiếu giới hạn maxlength và CSS overflow</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>Thêm if (length &gt;= 15) return và font scaling.</t>
+          <t>SEED-07</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Đổi dấu âm dương</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Màn hình chính / app.js</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>FR-13 (Đổi dấu số 0)</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Đổi dấu số 0 biến thành '-0' và nhảy thụt lề sang trái</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>1. Màn hình đang là 0
+2. Bấm phím ±</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Vẫn là 0 và giữ nguyên căn lề phải</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Hiển thị '-0' và bị thụt lề sang trái mép màn hình</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>https://quangpv021.github.io/calculator-qa-testing/assets/evidence_bug07.png</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>app.js (toggleSign) &amp; style.css</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>Trong đặc tả</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>BUG-08</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Trong đặc tả (FR-06)</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Nút Backspace (⌫) xóa ký tự cuối làm rỗng màn hình</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Màn hình có số 5 -&gt; bấm ⌫ -&gt; bấm +</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Màn hình trống rỗng '', bấm tiếp sinh NaN</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Màn hình phải quay về số 0 mặc định</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>Dòng 403: state.currentInput = '';</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>state.currentInput = '0';</t>
+          <t>SEED-08</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Nhật ký lịch sử</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Thanh bên phải (Sidebar)</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>FR-17 (Nhật ký lịch sử)</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Thẻ lịch sử tính toán bị vỡ khung và tràn thanh cuộn ngang khi biểu thức dài</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>1. Nhập 123456789 + 987654321 =
+2. Xem thẻ bên phải</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Biểu thức tự động ngắt dòng gọn gàng trong thẻ</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Bị tràn bề ngang gây méo mó khung lịch sử</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>https://quangpv021.github.io/calculator-qa-testing/assets/evidence_bug08.png</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>style.css (.history-expr)</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>Trong đặc tả</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>BUG-09</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Trong đặc tả (FR-10)</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Nhấn liên tiếp toán tử làm hỏng biểu thức (5 + × 2)</t>
+          <t>SEED-09</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Nhập 5 -&gt; bấm + -&gt; bấm × -&gt; nhập 2 -&gt; bấm =</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Toán tử bị nối chuỗi '5 + ×'</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Toán tử sau (×) tự động thay thế toán tử trước (+)</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>Dòng 333: state.operation = state.operation + ' ' + nextOp;</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>state.operation = nextOp; (ghi đè toán tử).</t>
+          <t>Chuẩn hóa nhập số</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Màn hình chính / app.js</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>FR-03 (Chặn số 0 đầu)</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Cho phép nhập nhiều số 0 vô nghĩa ở đầu (ví dụ: 0008)</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>1. Bấm 0 ba lần
+2. Bấm 8</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Chuẩn hóa hiển thị đúng số 8</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Màn hình hiển thị chuỗi '0008'</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>https://quangpv021.github.io/calculator-qa-testing/assets/evidence_bug09.png</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>app.js (inputDigit)</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>Trong đặc tả</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>BUG-10</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Trong đặc tả (FR-14)</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Tính phần trăm sai quy tắc: 100 + 10% ra 100.1</t>
+          <t>SEED-10</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Major</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Nhập 100 -&gt; bấm + -&gt; nhập 10 -&gt; bấm % -&gt; bấm =</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Tính ra 100.1 (chia 10 cho 100 rồi cộng)</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>110 (100 + 10% của 100)</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>Dòng 434: state.currentInput = `${val / 100}`;</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>Cộng phần trăm dựa trên số hạng thứ nhất.</t>
+          <t>Phép tính phần trăm</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Màn hình chính / app.js</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>FR-14 (Tính phần trăm)</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Nội dung công thức phần trăm sai: 100 + 10% ra 100.1 thay vì 110</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>1. Nhập 100 + 10 % =</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Kết quả hiển thị 110 (100 + 10% của 100)</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Màn hình tính 10% = 0.1 và cộng ra 100.1</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>https://quangpv021.github.io/calculator-qa-testing/assets/evidence_bug10.png</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>app.js (calcPercent)</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>Trong đặc tả</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>BUG-11</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Ngoài đặc tả (Edge)</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Nút 'C' (Clear Entry) xóa luôn biến nhớ Memory</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Lưu 50 vào MS -&gt; nhập 99 -&gt; bấm C -&gt; bấm MR</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>MR trả về 0 (bộ nhớ bị xóa trắng)</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>MR phải giữ nguyên giá trị 50 đã lưu</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>Dòng 413: state.memoryValue = 0; trong clearEntry()</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>Bỏ dòng xóa memoryValue, C chỉ xóa màn hình.</t>
+          <t>SEED-11</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Nhãn giao diện người dùng</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Nút C trên bàn phím</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Ngoài SRS (Nội dung nhãn tooltip)</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Nút C (Clear Entry) bị ghi sai Tooltip thành 'Clear All Data &amp; Memory'</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>1. Rê chuột lên nút C trên giao diện</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Tooltip hiển thị: 'Clear Entry (Xóa mục hiện tại)'</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Tooltip hiển thị sai lệch: 'Clear All Data &amp; Memory'</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>https://quangpv021.github.io/calculator-qa-testing/assets/evidence_bug11.png</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>index.html (nút #btnC)</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>Ngoài đặc tả</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>BUG-12</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Ngoài đặc tả (Logic)</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Nút 'M-' (Memory Subtract) tính ngược thành cộng</t>
+          <t>SEED-12</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Major</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Lưu 100 vào MS -&gt; nhập 30 -&gt; bấm M- -&gt; bấm MR</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>MR ra 130 (bị cộng dồn 30)</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>MR ra 70 (100 - 30)</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>Dòng 450: state.memoryValue += val; (nhầm dấu)</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>Đổi thành state.memoryValue -= val;</t>
+          <t>Hàm tính lũy thừa</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Màn hình chính / app.js</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>NFR-01 (Thời gian phản hồi &lt; 50ms)</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Đơ lag giao diện &gt; 3 giây khi tính bình phương do vòng lặp đồng bộ nặng</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>1. Nhập 5 -&gt; Bấm x²</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Kết quả 25 hiển thị tức thì (&lt; 10ms)</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Trình duyệt bị treo Main Thread &gt; 3.5 giây rồi mới phản hồi</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>https://quangpv021.github.io/calculator-qa-testing/assets/evidence_bug12.png</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>app.js (calcSquare)</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>Ngoài đặc tả</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>BUG-13</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Ngoài đặc tả (UI/UX)</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Đổi dấu số 0 biến thành số '-0'</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Màn hình đang là 0 -&gt; bấm nút ±</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>Màn hình hiển thị '-0'</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Vẫn giữ nguyên là '0'</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>Dòng 418: if (state.currentInput === '0') '-0'</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>if (state.currentInput === '0') return;</t>
+          <t>SEED-13</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Quản lý bộ nhớ RAM</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Lịch sử tính toán / app.js</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>NFR-02 (Giải phóng tài nguyên RAM)</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Rò rỉ bộ nhớ (Memory Leak) khi bấm Xóa lịch sử (dữ liệu không được giải phóng)</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>1. Tính 1+1=2 -&gt; Bấm Xóa lịch sử
+2. Tính 2+2=4</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Mảng dữ liệu được dọn sạch, chỉ còn 2+2=4</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Phép tính cũ 1+1=2 tự động phục hồi lại do mảng RAM không bị giải phóng</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>https://quangpv021.github.io/calculator-qa-testing/assets/evidence_bug13.png</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>app.js (clearHistory)</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>Ngoài đặc tả</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>BUG-14</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Ngoài đặc tả (State)</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Bấm phím '=' lần 2 bị reset kết quả về 0</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Bấm 5 + 2 = (kết quả 7) -&gt; bấm tiếp =</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Màn hình bị xóa về 0</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Lặp lại phép tính cuối: 7 + 2 = 9</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>Dòng 383: if (!state.operation) currentInput = '0';</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>Lưu lastOperation và lastOperand để tính lặp.</t>
+          <t>SEED-14</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Crash</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Chức năng xóa ký tự</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Màn hình chính / app.js</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>NFR-04 (Tính ổn định hệ thống)</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Sập ứng dụng (Crash / Freeze) khi xóa rỗng rồi bấm tính toán</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>1. Màn hình có số 5 -&gt; Bấm ⌫
+2. Bấm + -&gt; Bấm =</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Màn hình về 0 an toàn</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Ném ngoại lệ Uncaught TypeError, máy tính bị khóa đơ</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>https://quangpv021.github.io/calculator-qa-testing/assets/evidence_bug14.png</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>app.js (backspace &amp; calculate)</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>Ngoài đặc tả</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>BUG-15</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Ngoài đặc tả (Data)</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Xóa lịch sử (Clear History) bị rò rỉ dữ liệu cũ</t>
+          <t>SEED-15</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Crash</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
+          <t>Xử lý chuỗi toán tử</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Màn hình chính / app.js</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>NFR-04 (Tính ổn định hệ thống)</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Trắng màn hình (White Screen Fatal Crash) khi bấm liên tiếp toán tử sai</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>1. Bấm 8 -&gt; Bấm ÷ -&gt; Bấm × -&gt; Bấm =</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Báo lỗi cú pháp nhẹ nhàng</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Giao diện bị sập trắng xóa với lỗi 500 Unhandled Exception</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>https://quangpv021.github.io/calculator-qa-testing/assets/evidence_bug15.png</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>app.js (triggerFatalWhiteScreen)</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>Ngoài đặc tả</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>SEED-16</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Tính 1+1=2 -&gt; Bấm Xóa lịch sử -&gt; Tính tiếp 2+2=4</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>Phép tính cũ 1+1=2 tự động phục hồi lại</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Lịch sử chỉ lưu duy nhất 2+2=4</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>Dòng 473: comment out dòng state.historyData = []</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>Bỏ comment state.historyData = []; khi bấm xóa.</t>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Quản lý bộ nhớ tạm</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Bàn phím bộ nhớ / app.js</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Ngoài SRS (Logic phím M-)</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Nút 'M-' (Memory Subtract) tính ngược thành cộng dồn giá trị bộ nhớ</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>1. Lưu 100 vào MS
+2. Nhập 30 -&gt; Bấm M-
+3. Bấm MR</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>MR = 70 (100 - 30)</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>MR = 130 (bị cộng dồn 30 vào bộ nhớ)</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>https://quangpv021.github.io/calculator-qa-testing/assets/evidence_bug16.png</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>app.js (memorySubtract)</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>Ngoài đặc tả</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
